--- a/tests/serialisation_templates/datamodel/datamodel_template_v1.xlsx
+++ b/tests/serialisation_templates/datamodel/datamodel_template_v1.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Definitions!$A$1:$E$44</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Example(Library Model)'!$A$1:$AS$20</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Example(Library Model)'!$A$1:$AT$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="242">
   <si>
     <t xml:space="preserve">SubjectArea</t>
   </si>
@@ -209,12 +209,21 @@
     <t xml:space="preserve">The (primary) key used to reference the target entity by this relationship</t>
   </si>
   <si>
+    <t xml:space="preserve">RelationshipNamespace</t>
+  </si>
+  <si>
     <t xml:space="preserve">SourceRoleEntity</t>
   </si>
   <si>
+    <t xml:space="preserve">TargetEntityNamespace</t>
+  </si>
+  <si>
     <t xml:space="preserve">TargetRoleEntity</t>
   </si>
   <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
     <t xml:space="preserve">Party</t>
   </si>
   <si>
@@ -278,7 +287,7 @@
     <t xml:space="preserve">PartyRoleIdentifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Person Role Identifier</t>
+    <t xml:space="preserve">Party Role Identifier</t>
   </si>
   <si>
     <t xml:space="preserve">An internal identifier used to reference a specific Person-Role Context.</t>
@@ -407,9 +416,6 @@
     <t xml:space="preserve">assignsAuthorshipBy</t>
   </si>
   <si>
-    <t xml:space="preserve">FK-Author</t>
-  </si>
-  <si>
     <t xml:space="preserve">Library</t>
   </si>
   <si>
@@ -494,13 +500,40 @@
     <t xml:space="preserve">LibraryMembershipIdentifier</t>
   </si>
   <si>
-    <t xml:space="preserve">:ibrary Membership Identifier</t>
+    <t xml:space="preserve">Library Membership Identifier</t>
   </si>
   <si>
     <t xml:space="preserve">An internal identifier used to reference a specific membership relation between a Library and a person-acting as a member.</t>
   </si>
   <si>
     <t xml:space="preserve">Primary Key on LibraryMembership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reference to the Library that manages the Membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membership-Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">withLibrary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">managesMembership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reference to the PartyRole that identifies the member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membership-PartyRole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forMember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hasMembership</t>
   </si>
   <si>
     <t xml:space="preserve">Loan</t>
@@ -1421,15 +1454,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD26"/>
+  <dimension ref="A1:AT28"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.18"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="25.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.73"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.73"/>
@@ -1451,25 +1484,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="27.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="24.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="23.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="25.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="17.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="16.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="20.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="16.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="14.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="18.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="20.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="16.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="14.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="10.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="15.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="0" width="14.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="0" width="18.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="0" width="20.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="29" style="0" width="25.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="25.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="16.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="20.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="18.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="16.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="14.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="18.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="20.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="0" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="0" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="0" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="0" width="20.22"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="2" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>36</v>
       </c>
@@ -1555,1160 +1589,1312 @@
         <v>51</v>
       </c>
       <c r="AC1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="AH1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="AN1" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AO1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AT1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="XFD1" s="0"/>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N2" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O2" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P2" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="S2" s="0" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="U2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="W2" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="X2" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y2" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z2" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB2" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="W2" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="X2" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y2" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z2" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB2" s="0" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N3" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O3" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P3" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="R3" s="0" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V3" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W3" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X3" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y3" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z3" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB3" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="AB3" s="0" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N4" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O4" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R4" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="S4" s="0" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="U4" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V4" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="W4" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="X4" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y4" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z4" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB4" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF4" s="0"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N5" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O5" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="P5" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R5" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="W4" s="0" t="s">
+      <c r="S5" s="0" t="s">
         <v>68</v>
-      </c>
-      <c r="X4" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y4" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z4" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AB4" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE4" s="0"/>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O5" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="P5" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="R5" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="S5" s="0" t="s">
-        <v>65</v>
       </c>
       <c r="U5" s="0" t="n">
         <v>2</v>
       </c>
       <c r="V5" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="W5" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="X5" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y5" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z5" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB5" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="W5" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="X5" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y5" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z5" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB5" s="0" t="s">
-        <v>64</v>
-      </c>
       <c r="AC5" s="0" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="AD5" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE5" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH5" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI5" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ5" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK5" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="AG5" s="0" t="s">
+      <c r="AL5" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM5" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN5" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO5" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP5" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="AQ5" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="AR5" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS5" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT5" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N6" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="P6" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="S6" s="0" t="s">
         <v>79</v>
-      </c>
-      <c r="AH5" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI5" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="AJ5" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="AK5" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL5" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN5" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="AO5" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="AP5" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ5" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR5" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS5" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O6" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="P6" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="R6" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="S6" s="0" t="s">
-        <v>76</v>
       </c>
       <c r="U6" s="0" t="n">
         <v>3</v>
       </c>
       <c r="V6" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W6" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X6" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y6" s="0" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Z6" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB6" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC6" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD6" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE6" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH6" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI6" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="AJ6" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK6" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL6" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM6" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="AB6" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC6" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD6" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="AG6" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH6" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI6" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ6" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK6" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL6" s="0" t="s">
-        <v>91</v>
-      </c>
       <c r="AN6" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO6" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP6" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="AQ6" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="AR6" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="AO6" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="AP6" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="AQ6" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR6" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS6" s="0" t="n">
+      <c r="AS6" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT6" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N7" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O7" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="R7" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="U7" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V7" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W7" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X7" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y7" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z7" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB7" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="AB7" s="0" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N8" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O8" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="R8" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="U8" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V8" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W8" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X8" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y8" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z8" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB8" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="AB8" s="0" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N9" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" s="0" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O9" s="0" t="s">
+      <c r="P9" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="R9" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="S9" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="P9" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="R9" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="S9" s="0" t="s">
-        <v>102</v>
-      </c>
       <c r="T9" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="U9" s="0" t="n">
         <v>2</v>
       </c>
       <c r="V9" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W9" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X9" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y9" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Z9" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AB9" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AC9" s="0" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="AD9" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG9" s="0" t="s">
-        <v>105</v>
+        <v>118</v>
+      </c>
+      <c r="AE9" s="0" t="s">
+        <v>102</v>
       </c>
       <c r="AH9" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI9" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="AJ9" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK9" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="AI9" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="AJ9" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="AL9" s="0" t="s">
-        <v>91</v>
+      <c r="AM9" s="0" t="s">
+        <v>94</v>
       </c>
       <c r="AN9" s="0" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="AO9" s="0" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="AP9" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AQ9" s="0" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="AR9" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS9" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="AS9" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT9" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N10" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O10" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="P10" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="R10" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="S10" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="U10" s="0" t="n">
         <v>3</v>
       </c>
       <c r="V10" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W10" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X10" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y10" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Z10" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AB10" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC10" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD10" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE10" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="AH10" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI10" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ10" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK10" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM10" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN10" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO10" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="AC10" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="AD10" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="AG10" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="AH10" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="AI10" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="AJ10" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL10" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN10" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO10" s="0" t="s">
-        <v>124</v>
-      </c>
       <c r="AP10" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AQ10" s="0" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="AR10" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS10" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="AS10" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT10" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N11" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O11" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="R11" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="S11" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U11" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V11" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W11" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X11" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y11" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z11" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AB11" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N12" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O12" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="R12" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="S12" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="U12" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V12" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W12" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X12" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y12" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z12" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AB12" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N13" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O13" s="0" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O13" s="0" t="s">
-        <v>133</v>
-      </c>
       <c r="P13" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="R13" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S13" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="U13" s="0" t="n">
         <v>2</v>
       </c>
       <c r="V13" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W13" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X13" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y13" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Z13" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AB13" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AC13" s="0" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="AD13" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG13" s="0" t="s">
-        <v>133</v>
+        <v>142</v>
+      </c>
+      <c r="AE13" s="0" t="s">
+        <v>143</v>
       </c>
       <c r="AH13" s="0" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AI13" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AJ13" s="0" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="AK13" s="0" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="AL13" s="0" t="s">
-        <v>91</v>
+        <v>72</v>
+      </c>
+      <c r="AM13" s="0" t="s">
+        <v>94</v>
       </c>
       <c r="AN13" s="0" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="AO13" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP13" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AQ13" s="0" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="AR13" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS13" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="AS13" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT13" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N14" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O14" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P14" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="R14" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="S14" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="U14" s="0" t="n">
         <v>3</v>
       </c>
       <c r="V14" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W14" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X14" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y14" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Z14" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AB14" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC14" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD14" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="AE14" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="AH14" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI14" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ14" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="AK14" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="AL14" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM14" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN14" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO14" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="AC14" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="AD14" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="AG14" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="AH14" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="AI14" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="AJ14" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="AK14" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL14" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN14" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="AO14" s="0" t="s">
-        <v>150</v>
-      </c>
       <c r="AP14" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AQ14" s="0" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="AR14" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS14" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="AS14" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT14" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N15" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O15" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="R15" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="S15" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="U15" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V15" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W15" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X15" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y15" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z15" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AB15" s="0" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N16" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O16" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="P16" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R16" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="S16" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="U16" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="Z15" s="0" t="s">
+      <c r="W16" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="AA15" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB15" s="0" t="s">
+      <c r="X16" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y16" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z16" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB16" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="AC16" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD16" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE16" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH16" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI16" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ16" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="AK16" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="AL16" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM16" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN16" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO16" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP16" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="AQ16" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="AR16" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS16" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT16" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N17" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O17" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="P17" s="0" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O16" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="P16" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="R16" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="S16" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="U16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="W16" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="X16" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y16" s="0" t="s">
+      <c r="Q17" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="R17" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="S17" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="U17" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="Z16" s="0" t="s">
+      <c r="W17" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="AA16" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB16" s="0" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O17" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="P17" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="R17" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="S17" s="0" t="s">
+      <c r="X17" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y17" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z17" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB17" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC17" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD17" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="T17" s="1" t="s">
+      <c r="AE17" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="U17" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="W17" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="X17" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y17" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="Z17" s="0" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB17" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="AC17" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="AG17" s="0" t="s">
-        <v>158</v>
-      </c>
       <c r="AH17" s="0" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="AI17" s="0" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AJ17" s="0" t="s">
         <v>167</v>
       </c>
       <c r="AK17" s="0" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="AL17" s="0" t="s">
-        <v>91</v>
+        <v>72</v>
+      </c>
+      <c r="AM17" s="0" t="s">
+        <v>94</v>
       </c>
       <c r="AN17" s="0" t="s">
-        <v>151</v>
+        <v>64</v>
       </c>
       <c r="AO17" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP17" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="AQ17" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="AR17" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS17" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT17" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N18" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O18" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="P18" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="R18" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="S18" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="AP17" s="0" t="s">
+      <c r="T18" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="AQ17" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR17" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS17" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O18" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="P18" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="R18" s="0" t="s">
-        <v>177</v>
-      </c>
-      <c r="S18" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="U18" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V18" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W18" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X18" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y18" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z18" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB18" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N19" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O19" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="P19" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="R19" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="S19" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="T19" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="AA18" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AB18" s="0" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O19" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="P19" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="R19" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="S19" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="U19" s="0" t="n">
         <v>2</v>
       </c>
       <c r="V19" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W19" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X19" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y19" s="0" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="Z19" s="0" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AB19" s="0" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="AC19" s="0" t="s">
-        <v>184</v>
+        <v>64</v>
       </c>
       <c r="AD19" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="AG19" s="0" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="AH19" s="0" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="AI19" s="0" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="AJ19" s="0" t="s">
         <v>182</v>
       </c>
       <c r="AK19" s="0" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="AL19" s="0" t="s">
-        <v>91</v>
+        <v>72</v>
+      </c>
+      <c r="AM19" s="0" t="s">
+        <v>94</v>
       </c>
       <c r="AN19" s="0" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="AO19" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="AP19" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="AQ19" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="AR19" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS19" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT19" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N20" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O20" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="P20" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="R20" s="0" t="s">
         <v>188</v>
-      </c>
-      <c r="AP19" s="0" t="s">
-        <v>188</v>
-      </c>
-      <c r="AQ19" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR19" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS19" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O20" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="P20" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="R20" s="0" t="s">
-        <v>135</v>
       </c>
       <c r="S20" s="0" t="s">
         <v>189</v>
@@ -2717,428 +2903,609 @@
         <v>190</v>
       </c>
       <c r="U20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="W20" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="X20" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y20" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z20" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB20" s="0" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N21" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O21" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="P21" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="R21" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="S21" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="U21" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="W21" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="X21" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y21" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z21" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="AB21" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="AC21" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD21" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="AE21" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH21" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="AI21" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="AJ21" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="AK21" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL21" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM21" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN21" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO21" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="AP21" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="AQ21" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="AR21" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS21" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT21" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N22" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O22" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="P22" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="R22" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="S22" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="U22" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="V20" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="W20" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="X20" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y20" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="Z20" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB20" s="0" t="s">
+      <c r="V22" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="W22" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="X22" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y22" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z22" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB22" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC22" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD22" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="AE22" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="AC20" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="AD20" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="AG20" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="AH20" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="AI20" s="0" t="s">
-        <v>194</v>
-      </c>
-      <c r="AJ20" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="AK20" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL20" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN20" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="AO20" s="0" t="s">
-        <v>195</v>
-      </c>
-      <c r="AP20" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="AQ20" s="0" t="s">
+      <c r="AH22" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="AI22" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="AJ22" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="AK22" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="AL22" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM22" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN22" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO22" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="AP22" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ22" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="AR22" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS22" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT22" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N23" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O23" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="P23" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="R23" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="S23" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="U23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="AR20" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS20" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O21" s="0" t="s">
-        <v>197</v>
-      </c>
-      <c r="P21" s="0" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="R21" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="S21" s="0" t="s">
-        <v>201</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="U21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="W21" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="X21" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y21" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z21" s="0" t="s">
+      <c r="W23" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="AB21" s="0" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O22" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="P22" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="R22" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S22" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="U22" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="W22" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="X22" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y22" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z22" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB22" s="0" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O23" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="P23" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="R23" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="S23" s="0" t="s">
-        <v>201</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U23" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="W23" s="0" t="s">
-        <v>68</v>
-      </c>
       <c r="X23" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y23" s="0" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="Z23" s="0" t="s">
-        <v>210</v>
+        <v>74</v>
       </c>
       <c r="AB23" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="AC23" s="0" t="s">
         <v>211</v>
       </c>
-      <c r="AD23" s="0" t="s">
-        <v>212</v>
-      </c>
-      <c r="AG23" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="AH23" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="AI23" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="AJ23" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK23" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL23" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN23" s="0" t="s">
-        <v>197</v>
-      </c>
-      <c r="AO23" s="0" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N24" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O24" s="0" t="s">
         <v>214</v>
       </c>
-      <c r="AP23" s="0" t="s">
+      <c r="P24" s="0" t="s">
         <v>214</v>
       </c>
-      <c r="AQ23" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR23" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS23" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O24" s="0" t="s">
+      <c r="Q24" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="P24" s="0" t="s">
+      <c r="R24" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="Q24" s="1" t="s">
+      <c r="S24" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="R24" s="0" t="s">
+      <c r="T24" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="S24" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="U24" s="0" t="n">
         <v>1</v>
       </c>
       <c r="V24" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W24" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X24" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y24" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z24" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA24" s="1" t="s">
-        <v>221</v>
+        <v>74</v>
       </c>
       <c r="AB24" s="0" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N25" s="0" t="s">
+        <v>64</v>
+      </c>
       <c r="O25" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="P25" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q25" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="P25" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="R25" s="0" t="s">
-        <v>101</v>
+        <v>211</v>
       </c>
       <c r="S25" s="0" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="U25" s="0" t="n">
         <v>2</v>
       </c>
       <c r="V25" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W25" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X25" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="Y25" s="0" t="s">
-        <v>113</v>
+        <v>220</v>
       </c>
       <c r="Z25" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB25" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="AC25" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD25" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="AE25" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="AB25" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC25" s="0" t="s">
+      <c r="AH25" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="AI25" s="0" t="s">
         <v>224</v>
       </c>
-      <c r="AG25" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="AH25" s="0" t="s">
+      <c r="AJ25" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="AK25" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="AL25" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM25" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN25" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO25" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="AP25" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="AJ25" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="AK25" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL25" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN25" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="AO25" s="0" t="s">
+      <c r="AQ25" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="AR25" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS25" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT25" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N26" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O26" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="AQ25" s="0" t="s">
+      <c r="P26" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="R26" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="S26" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="U26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="AR25" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS25" s="0" t="n">
+      <c r="W26" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="X26" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y26" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z26" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA26" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB26" s="0" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N27" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O27" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="P27" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="R27" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="S27" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="U27" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="W27" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="X27" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y27" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z27" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="AB27" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC27" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD27" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="AH27" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="AI27" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="AK27" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="AL27" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM27" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN27" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO27" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="AP27" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR27" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS27" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT27" s="0" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O26" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="P26" s="0" t="s">
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N28" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="O28" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="P28" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="R28" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="Q26" s="1" t="s">
+      <c r="S28" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="R26" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="S26" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="U26" s="0" t="n">
+      <c r="T28" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="U28" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="V26" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="W26" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="X26" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y26" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="Z26" s="0" t="s">
-        <v>229</v>
-      </c>
-      <c r="AB26" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="AC26" s="0" t="s">
-        <v>230</v>
-      </c>
-      <c r="AG26" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="AH26" s="0" t="s">
-        <v>225</v>
-      </c>
-      <c r="AJ26" s="0" t="s">
-        <v>228</v>
-      </c>
-      <c r="AK26" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL26" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN26" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="AO26" s="0" t="s">
+      <c r="V28" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="W28" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="X28" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y28" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z28" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="AB28" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="AC28" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD28" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="AH28" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="AQ26" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR26" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS26" s="0" t="n">
+      <c r="AI28" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="AK28" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="AL28" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM28" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN28" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO28" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="AP28" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR28" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS28" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT28" s="0" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS20"/>
+  <autoFilter ref="A1:AT22"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/tests/serialisation_templates/datamodel/datamodel_template_v1.xlsx
+++ b/tests/serialisation_templates/datamodel/datamodel_template_v1.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Definitions!$A$1:$E$44</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Example(Library Model)'!$A$1:$AT$27</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Example(Library Model)'!$A$1:$AT$36</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">Primary Key on Asset</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference to the title that this asset is an instance of.</t>
+    <t xml:space="preserve">er</t>
   </si>
   <si>
     <t xml:space="preserve">Asset-Work</t>
@@ -1535,7 +1535,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="29" style="1" width="25.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="17.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="2" width="25.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="16.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="21.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="20.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="18.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="16.31"/>
@@ -3824,7 +3824,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT27"/>
+  <autoFilter ref="A1:AT36"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/tests/serialisation_templates/datamodel/datamodel_template_v1.xlsx
+++ b/tests/serialisation_templates/datamodel/datamodel_template_v1.xlsx
@@ -11,11 +11,14 @@
     <sheet name="Template" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Definitions" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Example(Library Model)" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Reference" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="EntitiesAttributes" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Relationships" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Reference" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Definitions!$A$1:$E$44</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Example(Library Model)'!$A$1:$AT$36</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Example(Library Model)'!$A$1:$AT$37</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Relationships!$A$1:$R$15</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="261">
   <si>
     <t xml:space="preserve">SubjectArea</t>
   </si>
@@ -263,6 +266,9 @@
     <t xml:space="preserve">Primary Key on Party</t>
   </si>
   <si>
+    <t xml:space="preserve">PartyIdentifier, Idx</t>
+  </si>
+  <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
@@ -272,6 +278,12 @@
     <t xml:space="preserve">Text</t>
   </si>
   <si>
+    <t xml:space="preserve">Idx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A secondary Identifier Part used as part of the index</t>
+  </si>
+  <si>
     <t xml:space="preserve">Role</t>
   </si>
   <si>
@@ -332,90 +344,399 @@
     <t xml:space="preserve">ContextParty</t>
   </si>
   <si>
+    <t xml:space="preserve">subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK-Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Key Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PartyRoleContext-RoleType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContextRole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A published work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An internal identifier used to reference a Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary key on Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The canonical title by which the work is known.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkAuthor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An attribution of an author to a work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkAuthorIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Author Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An internal identifier used to reference a specific instance of authorship.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Key on WorkAuthor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The identifier of the Title for which authorship is attributed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK-Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Key Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkAuthor-Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Author Context Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The identifier of the PersonAuthor context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK-PartyRoleContext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Key PartyRoleContext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkAuthor-Author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An instance of an organisation that holds books (assets) and makes them available on loan to members.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LibraryIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Library Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An internal identifier used to reference a specific Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Key on Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The name by which the library is known.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An instance of a physical asset that’s held by a Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AssetIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An internal identifier used to reference a specific Asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Key on Asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">er</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset-Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instanceOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference to the Library that manages this Asset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK-Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Key Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset-Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">managedBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LibraryMembership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Library Membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A person’s membership relation to a specific Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LibraryMembershipIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Library Membership Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An internal identifier used to reference a specific membership relation between a Library and a person-acting as a member.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Key on LibraryMembership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reference to the Library that manages the Membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membership-Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reference to the PartyRole that identifies the member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membership-PartyRole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An interval during which a member of a library borrows one or more Assets from a Library</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LoanIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An internal identifier used to reference a specific loan instance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Key on Loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LoanMember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The library member who took out the loan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK-LibraryMembership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Key LibraryMembership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan-Member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LoanItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An item that has been loaned out to a library member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LoanItemIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Item Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An internal identifier used to reference a specific item forming part of a loan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Key on LoanItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reference to the Loan that this LoanItem is a constituent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK-Loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Key Loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">part of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inventory Item Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A reference to the Asset that formed part of this loan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK-Asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Key Inventory Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">associatedAsset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassificationScheme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification Scheme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A formally described classification scheme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassificationSchemeIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification Scheme Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An internal identifier used to reference a ClassificationScheme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The name by which the classification scheme is known.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Classification applicable to a Work that forms part of a ClassificationScheme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClassificationIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An internal identifier used to reference a Classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference to the ClassificationScheme in which this Classification is defined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK-ClassificationScheme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Key to ClassificationScheme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">definedBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">defined by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The name or reference by which the classification is known within its classification scheme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A description of the classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkClassification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A classification statement applied to a work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WorkClassificationIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Classification Identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An internal identifier used to reference an instance of a classification applied to a work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Key on WorkClassification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Work to which this classification is applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Key to Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assignedTo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The classification that is applied to the work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK-Classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foreign Key to Classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">classifiedBy</t>
+  </si>
+  <si>
     <t xml:space="preserve">involves</t>
   </si>
   <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
     <t xml:space="preserve">playsAs</t>
   </si>
   <si>
-    <t xml:space="preserve">FK-Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foreign Key Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PartyRoleContext-RoleType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContextRole</t>
-  </si>
-  <si>
     <t xml:space="preserve">withRole</t>
   </si>
   <si>
     <t xml:space="preserve">setsContextFor</t>
   </si>
   <si>
-    <t xml:space="preserve">Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A published work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WorkIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal identifier used to reference a Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary key on Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The canonical title by which the work is known.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WorkAuthor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work Author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An attribution of an author to a work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WorkAuthorIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work Author Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal identifier used to reference a specific instance of authorship.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Key on WorkAuthor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The identifier of the Title for which authorship is attributed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK-Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foreign Key Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WorkAuthor-Work</t>
-  </si>
-  <si>
     <t xml:space="preserve">assignsAuthorshipFor</t>
   </si>
   <si>
@@ -425,186 +746,33 @@
     <t xml:space="preserve">Written By</t>
   </si>
   <si>
-    <t xml:space="preserve">Author Context Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The identifier of the PersonAuthor context</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK-PartyRoleContext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foreign Key PartyRoleContext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WorkAuthor-Author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Author</t>
-  </si>
-  <si>
     <t xml:space="preserve">assignsAuthorshipBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An instance of an organisation that holds books (assets) and makes them available on loan to members.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LibraryIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Library Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal identifier used to reference a specific Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Key on Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The name by which the library is known.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An instance of a physical asset that’s held by a Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AssetIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal identifier used to reference a specific Asset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Key on Asset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">er</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset-Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instanceOf</t>
-  </si>
-  <si>
     <t xml:space="preserve">isInstanceOf</t>
   </si>
   <si>
     <t xml:space="preserve">instance of</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference to the Library that manages this Asset.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK-Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foreign Key Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset-Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">managedBy</t>
-  </si>
-  <si>
     <t xml:space="preserve">managed by</t>
   </si>
   <si>
     <t xml:space="preserve">manages</t>
   </si>
   <si>
-    <t xml:space="preserve">LibraryMembership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Library Membership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A person’s membership relation to a specific Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LibraryMembershipIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Library Membership Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal identifier used to reference a specific membership relation between a Library and a person-acting as a member.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Key on LibraryMembership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A reference to the Library that manages the Membership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Membership-Library</t>
-  </si>
-  <si>
     <t xml:space="preserve">withLibrary</t>
   </si>
   <si>
     <t xml:space="preserve">managesMembership</t>
   </si>
   <si>
-    <t xml:space="preserve">A reference to the PartyRole that identifies the member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Membership-PartyRole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Member</t>
-  </si>
-  <si>
     <t xml:space="preserve">forMember</t>
   </si>
   <si>
     <t xml:space="preserve">hasMembership</t>
   </si>
   <si>
-    <t xml:space="preserve">Loan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An interval during which a member of a library borrows one or more Assets from a Library</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LoanIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal identifier used to reference a specific loan instance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Key on Loan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LoanMember</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan Member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The library member who took out the loan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK-LibraryMembership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foreign Key LibraryMembership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan-Member</t>
-  </si>
-  <si>
     <t xml:space="preserve">loanedBy</t>
   </si>
   <si>
@@ -617,42 +785,6 @@
     <t xml:space="preserve">takes out</t>
   </si>
   <si>
-    <t xml:space="preserve">LoanItem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An item that has been loaned out to a library member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LoanItemIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan Item Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal identifier used to reference a specific item forming part of a loan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Key on LoanItem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A reference to the Loan that this LoanItem is a constituent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK-Loan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foreign Key Loan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">part of</t>
-  </si>
-  <si>
     <t xml:space="preserve">isPartOf</t>
   </si>
   <si>
@@ -662,21 +794,6 @@
     <t xml:space="preserve">contains</t>
   </si>
   <si>
-    <t xml:space="preserve">Inventory Item Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A reference to the Asset that formed part of this loan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK-Asset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foreign Key Inventory Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">associatedAsset</t>
-  </si>
-  <si>
     <t xml:space="preserve">specifies</t>
   </si>
   <si>
@@ -686,115 +803,16 @@
     <t xml:space="preserve">specified by</t>
   </si>
   <si>
-    <t xml:space="preserve">ClassificationScheme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classification Scheme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A formally described classification scheme.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ClassificationSchemeIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classification Scheme Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal identifier used to reference a ClassificationScheme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The name by which the classification scheme is known.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Classification applicable to a Work that forms part of a ClassificationScheme.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ClassificationIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classification Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal identifier used to reference a Classification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference to the ClassificationScheme in which this Classification is defined</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK-ClassificationScheme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foreign Key to ClassificationScheme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">definedBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defined by</t>
-  </si>
-  <si>
     <t xml:space="preserve">isDefinedBy</t>
   </si>
   <si>
     <t xml:space="preserve">defines</t>
   </si>
   <si>
-    <t xml:space="preserve">The name or reference by which the classification is known within its classification scheme.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A description of the classification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WorkClassification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work Classification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A classification statement applied to a work.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WorkClassificationIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Work Classification Identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An internal identifier used to reference an instance of a classification applied to a work.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary Key on WorkClassification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Work to which this classification is applied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foreign Key to Work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assignedTo</t>
-  </si>
-  <si>
     <t xml:space="preserve">source</t>
   </si>
   <si>
     <t xml:space="preserve">target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The classification that is applied to the work.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FK-Classification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foreign Key to Classification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">classifiedBy</t>
   </si>
 </sst>
 </file>
@@ -927,6 +945,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -1502,7 +1524,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AT36"/>
+  <dimension ref="A1:AT37"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.45"/>
@@ -1735,7 +1757,7 @@
         <v>77</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1752,13 +1774,13 @@
         <v>68</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U3" s="1" t="n">
         <v>2</v>
@@ -1767,54 +1789,39 @@
         <v>72</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N4" s="1" t="s">
         <v>66</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="U4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1822,34 +1829,46 @@
         <v>66</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U5" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V5" s="1" t="s">
         <v>72</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>74</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1857,31 +1876,34 @@
         <v>66</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="P6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="U6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>80</v>
+      <c r="X6" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1889,70 +1911,57 @@
         <v>66</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="P7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="S7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="U7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="U7" s="1" t="n">
+      <c r="R8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AF7" s="1"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="U8" s="1" t="n">
-        <v>2</v>
       </c>
       <c r="V8" s="1" t="s">
         <v>72</v>
@@ -1964,84 +1973,40 @@
         <v>74</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>98</v>
+        <v>76</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH8" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI8" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ8" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AP8" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AQ8" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AR8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT8" s="1" t="n">
-        <v>1</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AF8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N9" s="1" t="s">
         <v>66</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>72</v>
@@ -2053,52 +2018,52 @@
         <v>74</v>
       </c>
       <c r="Y9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="Z9" s="1" t="s">
+      <c r="AJ9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM9" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AB9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD9" s="1" t="s">
+      <c r="AN9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AE9" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AH9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK9" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AL9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM9" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP9" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="AQ9" s="1" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="AR9" s="1" t="s">
         <v>75</v>
@@ -2115,25 +2080,22 @@
         <v>66</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V10" s="1" t="s">
         <v>72</v>
@@ -2145,16 +2107,61 @@
         <v>74</v>
       </c>
       <c r="Y10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AL10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Z10" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AB10" s="1" t="s">
-        <v>112</v>
+      <c r="AS10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT10" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2162,81 +2169,81 @@
         <v>66</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="R11" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="T11" s="2" t="s">
+      <c r="P12" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="U11" s="1" t="n">
+      <c r="S12" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="U12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="V12" s="1" t="s">
         <v>72</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="X12" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AB12" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2244,25 +2251,25 @@
         <v>66</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U13" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V13" s="1" t="s">
         <v>72</v>
@@ -2274,84 +2281,42 @@
         <v>74</v>
       </c>
       <c r="Y13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="T14" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="Z13" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB13" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC13" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD13" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AE13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH13" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AI13" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ13" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AK13" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM13" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN13" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP13" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AQ13" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AR13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS13" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT13" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="U14" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V14" s="1" t="s">
         <v>72</v>
@@ -2363,49 +2328,49 @@
         <v>74</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="AC14" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AI14" s="1" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="AK14" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AN14" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AO14" s="1" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="AP14" s="1" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="AQ14" s="1" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="AR14" s="1" t="s">
         <v>75</v>
@@ -2417,30 +2382,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N15" s="1" t="s">
         <v>66</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="U15" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V15" s="1" t="s">
         <v>72</v>
@@ -2452,16 +2417,58 @@
         <v>74</v>
       </c>
       <c r="Y15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AE15" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH15" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AM15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Z15" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA15" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="AB15" s="1" t="s">
-        <v>141</v>
+      <c r="AS15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT15" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2469,78 +2476,78 @@
         <v>66</v>
       </c>
       <c r="O16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="P16" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="R16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="U16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="U17" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N17" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="U17" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="V17" s="1" t="s">
         <v>72</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z17" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA17" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="AB17" s="1" t="s">
-        <v>148</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2548,25 +2555,25 @@
         <v>66</v>
       </c>
       <c r="O18" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="P18" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="R18" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="U18" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V18" s="1" t="s">
         <v>72</v>
@@ -2578,61 +2585,16 @@
         <v>74</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>127</v>
+        <v>76</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD18" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AE18" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="AH18" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AI18" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="AJ18" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AK18" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM18" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AQ18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR18" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT18" s="1" t="n">
-        <v>1</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2640,25 +2602,25 @@
         <v>66</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="U19" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V19" s="1" t="s">
         <v>72</v>
@@ -2670,52 +2632,52 @@
         <v>74</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="AC19" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AD19" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AH19" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AI19" s="1" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="AJ19" s="1" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="AK19" s="1" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="AL19" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AN19" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AO19" s="1" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="AP19" s="1" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="AQ19" s="1" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="AR19" s="1" t="s">
         <v>75</v>
@@ -2727,30 +2689,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N20" s="1" t="s">
         <v>66</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="U20" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>72</v>
@@ -2762,42 +2724,87 @@
         <v>74</v>
       </c>
       <c r="Y20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM20" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO20" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AP20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Z20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA20" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AB20" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AS20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT20" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N21" s="1" t="s">
         <v>66</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="U21" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V21" s="1" t="s">
         <v>72</v>
@@ -2809,87 +2816,42 @@
         <v>74</v>
       </c>
       <c r="Y21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Z21" s="1" t="s">
+      <c r="Q22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="AB21" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD21" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE21" s="1" t="s">
+      <c r="R22" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AH21" s="1" t="s">
+      <c r="T22" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="AI21" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AJ21" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AK21" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AL21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM21" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO21" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AP21" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="AQ21" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="AR21" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT21" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="U22" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V22" s="1" t="s">
         <v>72</v>
@@ -2901,52 +2863,52 @@
         <v>74</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="AC22" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="AH22" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="AI22" s="1" t="s">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="AJ22" s="1" t="s">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="AK22" s="1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="AL22" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AN22" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AO22" s="1" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="AP22" s="1" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="AQ22" s="1" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="AR22" s="1" t="s">
         <v>75</v>
@@ -2958,30 +2920,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N23" s="1" t="s">
         <v>66</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>183</v>
+        <v>97</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="U23" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V23" s="1" t="s">
         <v>72</v>
@@ -2993,16 +2955,61 @@
         <v>74</v>
       </c>
       <c r="Y23" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK23" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AL23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR23" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Z23" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA23" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB23" s="1" t="s">
-        <v>182</v>
+      <c r="AS23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT23" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3010,25 +3017,25 @@
         <v>66</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="U24" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24" s="1" t="s">
         <v>72</v>
@@ -3040,84 +3047,42 @@
         <v>74</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>190</v>
+        <v>76</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="AC24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD24" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="AH24" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AI24" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="AJ24" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AK24" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="AL24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM24" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO24" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="AP24" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="AQ24" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="AR24" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT24" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="N25" s="1" t="s">
         <v>66</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="U25" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" s="1" t="s">
         <v>72</v>
@@ -3129,16 +3094,58 @@
         <v>74</v>
       </c>
       <c r="Y25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="AL25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO25" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AP25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Z25" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA25" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="AB25" s="1" t="s">
-        <v>199</v>
+      <c r="AS25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT25" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3146,25 +3153,25 @@
         <v>66</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="U26" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26" s="1" t="s">
         <v>72</v>
@@ -3176,61 +3183,16 @@
         <v>74</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>205</v>
+        <v>184</v>
+      </c>
+      <c r="AA26" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="AC26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD26" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="AE26" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="AH26" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="AI26" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ26" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="AK26" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="AL26" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM26" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO26" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AP26" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="AQ26" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR26" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS26" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT26" s="1" t="n">
-        <v>1</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3238,25 +3200,25 @@
         <v>66</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="U27" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V27" s="1" t="s">
         <v>72</v>
@@ -3268,52 +3230,52 @@
         <v>74</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="AC27" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AD27" s="1" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="AH27" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="AI27" s="1" t="s">
-        <v>216</v>
+        <v>104</v>
       </c>
       <c r="AJ27" s="1" t="s">
-        <v>216</v>
+        <v>104</v>
       </c>
       <c r="AK27" s="1" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="AL27" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AN27" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AO27" s="1" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="AP27" s="1" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
       <c r="AQ27" s="1" t="s">
-        <v>218</v>
+        <v>106</v>
       </c>
       <c r="AR27" s="1" t="s">
         <v>75</v>
@@ -3330,25 +3292,25 @@
         <v>66</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>222</v>
+        <v>145</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="U28" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V28" s="1" t="s">
         <v>72</v>
@@ -3360,13 +3322,61 @@
         <v>74</v>
       </c>
       <c r="Y28" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD28" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AH28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AI28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK28" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="AL28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO28" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AP28" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ28" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR28" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Z28" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB28" s="1" t="s">
-        <v>222</v>
+      <c r="AS28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT28" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3374,34 +3384,43 @@
         <v>66</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="U29" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="1" t="s">
         <v>72</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="X29" s="1" t="s">
         <v>74</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB29" s="1" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3409,69 +3428,60 @@
         <v>66</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>228</v>
+        <v>79</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="U30" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U31" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="V30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB30" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N31" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="U31" s="1" t="n">
-        <v>2</v>
       </c>
       <c r="V31" s="1" t="s">
         <v>72</v>
@@ -3483,61 +3493,13 @@
         <v>74</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>232</v>
+        <v>75</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>233</v>
+        <v>76</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="AC31" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD31" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="AE31" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="AH31" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="AI31" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="AJ31" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="AK31" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="AL31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM31" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN31" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO31" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AP31" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="AQ31" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="AR31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT31" s="1" t="n">
-        <v>1</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3545,142 +3507,187 @@
         <v>66</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="U32" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y32" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB32" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AC32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD32" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="AE32" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="AH32" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="AI32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ32" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK32" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AL32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM32" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO32" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="AP32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AS32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT32" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="U33" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="V32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="X32" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="T33" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="U33" s="1" t="n">
+      <c r="V33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="U34" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="V33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="X33" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="T34" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="U34" s="1" t="n">
+      <c r="V34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="U35" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X34" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y34" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z34" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA34" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="AB34" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N35" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T35" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="U35" s="1" t="n">
-        <v>2</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>72</v>
@@ -3692,52 +3699,16 @@
         <v>74</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>248</v>
+        <v>76</v>
+      </c>
+      <c r="AA35" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="AB35" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC35" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD35" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="AH35" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="AI35" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="AK35" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL35" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AM35" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN35" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AO35" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP35" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="AR35" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AS35" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT35" s="1" t="n">
-        <v>1</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3745,25 +3716,25 @@
         <v>66</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>228</v>
+        <v>113</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>229</v>
+        <v>114</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="U36" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>72</v>
@@ -3775,43 +3746,49 @@
         <v>74</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>253</v>
+        <v>127</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>228</v>
+        <v>113</v>
       </c>
       <c r="AC36" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AD36" s="1" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="AH36" s="1" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="AI36" s="1" t="s">
-        <v>250</v>
+        <v>104</v>
+      </c>
+      <c r="AJ36" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="AK36" s="1" t="s">
-        <v>253</v>
+        <v>127</v>
       </c>
       <c r="AL36" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AM36" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AN36" s="1" t="s">
         <v>66</v>
       </c>
       <c r="AO36" s="1" t="s">
-        <v>226</v>
+        <v>111</v>
       </c>
       <c r="AP36" s="1" t="s">
-        <v>251</v>
+        <v>106</v>
+      </c>
+      <c r="AQ36" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="AR36" s="1" t="s">
         <v>75</v>
@@ -3823,8 +3800,97 @@
         <v>1</v>
       </c>
     </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="U37" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="Z37" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB37" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AC37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD37" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH37" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="AI37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="AL37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM37" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO37" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="AP37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AQ37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AR37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AS37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT37" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AT36"/>
+  <autoFilter ref="A1:AT37"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3841,6 +3907,2429 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:AB36"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="23.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.73"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="6.85"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="23.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="23.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="24.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="2" width="23.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="17.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="25.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="13.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="24.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="34.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="2" width="24.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="23.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="U8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="U9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="U10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="U11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="U12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="U13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="U14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="U15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA15" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="U16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="U18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="U19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA20" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="U21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="U22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="U23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB23" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="U24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="U25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA25" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="U26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="AB26" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB27" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="U28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="U29" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB30" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="U31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="AB31" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="U32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="U33" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="U34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA34" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB34" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="U35" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z35" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="AB35" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N36" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="U36" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y36" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="Z36" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB36" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:R15"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="19.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="19.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="23.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="23.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="24.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="19.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="18.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="22.99"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R15"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
